--- a/AIGGPA_Fieldwork_Review/05_AIGGPA_Master_CrossTabs_CadreDivide.xlsx
+++ b/AIGGPA_Fieldwork_Review/05_AIGGPA_Master_CrossTabs_CadreDivide.xlsx
@@ -508,10 +508,10 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>2.08</v>
+        <v>1.99</v>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
@@ -531,10 +531,10 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>3.03</v>
+        <v>3.01</v>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
@@ -554,10 +554,10 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>2.96</v>
+        <v>3.33</v>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
@@ -577,10 +577,10 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>3.74</v>
+        <v>3.77</v>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
@@ -672,27 +672,27 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>140</v>
+        <v>13</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>3.09</v>
+        <v>4.42</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>3.21</v>
+        <v>4.46</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>3.02</v>
+        <v>4.85</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>3.04</v>
+        <v>1.08</v>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>44%</t>
+          <t>92%</t>
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>2.64</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -702,27 +702,27 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>0</v>
+        <v>4.13</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>73%</t>
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
     </row>
     <row r="6">
@@ -732,27 +732,27 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>44%</t>
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
     </row>
     <row r="7">
@@ -762,27 +762,27 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0</v>
+        <v>4.52</v>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>7%</t>
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
     </row>
   </sheetData>
